--- a/LISTAS_ORDENADAS/MA/Cerrojos Pasadores/PASADOR BOLT.xlsx
+++ b/LISTAS_ORDENADAS/MA/Cerrojos Pasadores/PASADOR BOLT.xlsx
@@ -781,14 +781,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="n">
-        <v>45216.53895210211</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -834,21 +830,6 @@
       </c>
       <c r="E11" s="11" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="1">
       <c r="A27" s="21" t="inlineStr">
         <is>
@@ -880,7 +861,7 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="16" t="n">
-        <v>646.84</v>
+        <v>534.582</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="1">
@@ -896,7 +877,7 @@
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="15" t="n">
-        <v>668.97</v>
+        <v>552.874</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="1">
@@ -912,7 +893,7 @@
       </c>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="16" t="n">
-        <v>680.87</v>
+        <v>562.708</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="1">
@@ -928,7 +909,7 @@
       </c>
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="16" t="n">
-        <v>701.3</v>
+        <v>579.591</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="1">
@@ -944,7 +925,7 @@
       </c>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="16" t="n">
-        <v>1004.31</v>
+        <v>830.009</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="1">
@@ -960,7 +941,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>968.53</v>
+        <v>800.441</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="1">
@@ -976,7 +957,7 @@
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="16" t="n">
-        <v>1353.25</v>
+        <v>1118.395</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="1">
@@ -992,10 +973,9 @@
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="15" t="n">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="36"/>
+        <v>1147.937</v>
+      </c>
+    </row>
     <row r="37" ht="18" customHeight="1" s="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
@@ -1007,8 +987,6 @@
     <row r="38" ht="18" customHeight="1" s="1">
       <c r="E38" s="4" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -1018,19 +996,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
